--- a/docs/Tablas Movimientos.xlsx
+++ b/docs/Tablas Movimientos.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documentos\Proyectos\FinanKore\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documentos\Proyectos\FinanKore\Financore\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{148F003E-DA48-4BE7-B529-2C66090A7581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7A83AB2-AB36-4412-B771-312078A3176A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{57ED79E0-A070-4370-834F-0964443A1EE9}"/>
+    <workbookView xWindow="-2544" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{57ED79E0-A070-4370-834F-0964443A1EE9}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>

--- a/docs/Tablas Movimientos.xlsx
+++ b/docs/Tablas Movimientos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documentos\Proyectos\FinanKore\Financore\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documentos\Proyectos\FinanKore\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7A83AB2-AB36-4412-B771-312078A3176A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96602D80-2E1D-48E7-9407-5000B89F97CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-2544" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{57ED79E0-A070-4370-834F-0964443A1EE9}"/>
+    <workbookView xWindow="19110" yWindow="-10760" windowWidth="19380" windowHeight="20970" xr2:uid="{57ED79E0-A070-4370-834F-0964443A1EE9}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="38">
   <si>
     <t>Id</t>
   </si>
@@ -138,6 +138,18 @@
   </si>
   <si>
     <t>ProyectoId</t>
+  </si>
+  <si>
+    <t>Categoria</t>
+  </si>
+  <si>
+    <t>Casa</t>
+  </si>
+  <si>
+    <t>Dani</t>
+  </si>
+  <si>
+    <t>Actsis</t>
   </si>
 </sst>
 </file>
@@ -167,7 +179,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -204,6 +216,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -217,7 +235,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -232,6 +250,10 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -585,7 +607,7 @@
       <c r="B2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="11" t="s">
         <v>22</v>
       </c>
     </row>
@@ -688,6 +710,9 @@
       <c r="G8" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="I8" s="11" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B9" s="3">
@@ -696,7 +721,7 @@
       <c r="C9" s="9">
         <v>1</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="10">
         <v>1</v>
       </c>
       <c r="E9" t="s">
@@ -708,6 +733,12 @@
       <c r="G9">
         <v>-100</v>
       </c>
+      <c r="I9" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B10" s="3">
@@ -716,7 +747,7 @@
       <c r="C10" s="9">
         <v>1</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="10">
         <v>2</v>
       </c>
       <c r="E10" t="s">
@@ -727,6 +758,12 @@
       </c>
       <c r="G10">
         <v>-1500</v>
+      </c>
+      <c r="I10" s="10">
+        <v>1</v>
+      </c>
+      <c r="J10" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.3">
@@ -736,7 +773,7 @@
       <c r="C11" s="9">
         <v>1</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="10">
         <v>8</v>
       </c>
       <c r="E11" t="s">
@@ -747,6 +784,12 @@
       </c>
       <c r="G11">
         <v>6600</v>
+      </c>
+      <c r="I11" s="10">
+        <v>2</v>
+      </c>
+      <c r="J11" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.3">
@@ -756,7 +799,7 @@
       <c r="C12" s="9">
         <v>1</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="10">
         <v>4</v>
       </c>
       <c r="E12" t="s">
@@ -767,6 +810,20 @@
       </c>
       <c r="G12">
         <v>-100</v>
+      </c>
+      <c r="I12" s="10">
+        <v>8</v>
+      </c>
+      <c r="J12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="I13" s="10">
+        <v>4</v>
+      </c>
+      <c r="J13" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.3">
